--- a/sales-report.xlsx
+++ b/sales-report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/onbozoyan/Downloads/report-generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14289FC5-1CE6-3942-9084-81143237FE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37090526-6C44-2F41-A24A-9D7D07A13C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="2160" windowWidth="28040" windowHeight="17440" xr2:uid="{8EE46694-27A0-8048-B457-EF6458B9856F}"/>
   </bookViews>
@@ -35,9 +35,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>blank</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+  <si>
+    <t>{{token}}</t>
+  </si>
+  <si>
+    <t>Sales report: {{period}}</t>
+  </si>
+  <si>
+    <t>[[TABLE_START:rows]]</t>
+  </si>
+  <si>
+    <t>{{item.name}}</t>
+  </si>
+  <si>
+    <t>{{item.amount}}</t>
+  </si>
+  <si>
+    <t>[[TABLE_END:rows]]</t>
+  </si>
+  <si>
+    <t>Total: {{total}}</t>
+  </si>
+  <si>
+    <t>Sales report: 2026-Q1</t>
+  </si>
+  <si>
+    <t>TemplateInput[fileName=Book1.xlsx, contentType=null, bytes=[B@3701eaf6]</t>
+  </si>
+  <si>
+    <t>Total: 4550.75</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -45,13 +75,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF806C"/>
+      <name val="Monaco"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -74,8 +110,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -390,12 +427,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219F9550-F4D0-054E-8000-8E802D1DB356}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s" s="0">
-        <v>0</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/sales-report.xlsx
+++ b/sales-report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/onbozoyan/Downloads/report-generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37090526-6C44-2F41-A24A-9D7D07A13C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6321F1B4-30E8-3743-8B67-6EA391F97D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="2160" windowWidth="28040" windowHeight="17440" xr2:uid="{8EE46694-27A0-8048-B457-EF6458B9856F}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>{{token}}</t>
   </si>
@@ -58,16 +58,37 @@
     <t>Total: {{total}}</t>
   </si>
   <si>
+    <t>{{TABLE_HERE}}</t>
+  </si>
+  <si>
     <t>Sales report: 2026-Q1</t>
   </si>
   <si>
-    <t>TemplateInput[fileName=Book1.xlsx, contentType=null, bytes=[B@3701eaf6]</t>
+    <t>TemplateInput[fileName=Book1.xlsx, contentType=null, bytes=[B@2758fe70]</t>
   </si>
   <si>
     <t>Total: 4550.75</t>
   </si>
   <si>
+    <t>жопа</t>
+  </si>
+  <si>
     <t/>
+  </si>
+  <si>
+    <t>слона</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>North</t>
   </si>
 </sst>
 </file>
@@ -427,46 +448,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219F9550-F4D0-054E-8000-8E802D1DB356}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2" ht="16.0" customHeight="true">
+      <c r="F7" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="16.0" customHeight="true">
+      <c r="F8" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>900.0</v>
+      </c>
+      <c r="H8" s="0"/>
+      <c r="I8" s="0"/>
+    </row>
+    <row r="9" ht="16.0" customHeight="true">
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>900.0</v>
+      </c>
+    </row>
+    <row r="10" ht="16.0" customHeight="true">
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>1200.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
